--- a/check_in_forms/049_hospital_patient_status_check_in_form--check_in_forms.xlsx
+++ b/check_in_forms/049_hospital_patient_status_check_in_form--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_status_update</t>
+          <t>patient_status_update_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Patient Status Update</t>
+          <t>Patient Status Update 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>status_update_date</t>
+          <t>status_update_date_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Status Update Date</t>
+          <t>Status Update Date 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>status_update_time</t>
+          <t>status_update_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Status Update Time</t>
+          <t>Status Update Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>patient_status_update</t>
+          <t>patient_status_update_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patient Status Update</t>
+          <t>Patient Status Update 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>status_update_date</t>
+          <t>status_update_date_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Status Update Date</t>
+          <t>Status Update Date 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>status_update_time</t>
+          <t>status_update_time_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Status Update Time</t>
+          <t>Status Update Time 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
